--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_salud.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12064,7 +12064,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14404,7 +14404,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15405,7 +15405,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16485,7 +16485,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16716,7 +16716,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17794,7 +17794,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18736,7 +18736,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18894,7 +18894,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19052,7 +19052,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19289,7 +19289,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20079,7 +20079,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20395,7 +20395,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20948,7 +20948,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21260,7 +21260,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21568,7 +21568,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21722,7 +21722,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21799,7 +21799,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21876,7 +21876,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21953,7 +21953,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22261,7 +22261,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22492,7 +22492,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22569,7 +22569,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22723,7 +22723,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23108,7 +23108,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23262,7 +23262,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23416,7 +23416,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23955,7 +23955,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25033,7 +25033,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25264,7 +25264,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25418,7 +25418,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25495,7 +25495,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25649,7 +25649,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25884,7 +25884,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25963,7 +25963,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26585,7 +26585,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26893,7 +26893,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27047,7 +27047,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27201,7 +27201,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27355,7 +27355,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27432,7 +27432,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27586,7 +27586,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27740,7 +27740,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28125,7 +28125,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28202,7 +28202,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28356,7 +28356,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28433,7 +28433,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28510,7 +28510,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28664,7 +28664,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28818,7 +28818,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28895,7 +28895,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -28972,7 +28972,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29049,7 +29049,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29588,7 +29588,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29896,7 +29896,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30204,7 +30204,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30281,7 +30281,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30358,7 +30358,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30435,7 +30435,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30512,7 +30512,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30589,7 +30589,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30820,7 +30820,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -30899,7 +30899,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31136,7 +31136,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31215,7 +31215,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31294,7 +31294,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31371,7 +31371,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31606,7 +31606,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31685,7 +31685,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31764,7 +31764,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -31922,7 +31922,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32080,7 +32080,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32396,7 +32396,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32554,7 +32554,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33028,7 +33028,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33107,7 +33107,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33186,7 +33186,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33344,7 +33344,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33423,7 +33423,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33581,7 +33581,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33660,7 +33660,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33739,7 +33739,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33818,7 +33818,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -33976,7 +33976,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34055,7 +34055,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34213,7 +34213,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34292,7 +34292,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34450,7 +34450,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34529,7 +34529,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34608,7 +34608,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34687,7 +34687,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34766,7 +34766,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34845,7 +34845,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -34924,7 +34924,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35082,7 +35082,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35240,7 +35240,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35319,7 +35319,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35477,7 +35477,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35556,7 +35556,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35635,7 +35635,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35714,7 +35714,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35793,7 +35793,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -35872,7 +35872,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -35951,7 +35951,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36030,7 +36030,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36109,7 +36109,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36188,7 +36188,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36267,7 +36267,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36346,7 +36346,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36425,7 +36425,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36504,7 +36504,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36583,7 +36583,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36660,7 +36660,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36745,7 +36745,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
